--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1031,6 +1031,10 @@
     <t>DICOM-objekt. För att ge renderbar data som kan visas på det sätt som användaren önskar (med hjälp av en viewer/renderare) ges möjligheten att skicka med binärdata eller en URI till ett DICOM-objekt i någon av SOP-klasserna för Bild. Både imageDicomData och ImageStaticData kan, och om möjligt bör anges för att underlätta för konsument.</t>
   </si>
   <si>
+    <t>getimagingoutcome-dicom-choice:Ett och endast ett av dicomValue och dicomReference ska anges {dicomValue.exists() xor dicomReference.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>SEEHDSLMImagingOutcome.imagingOutcome.imagingOutcomeBody.imageRecording.imageDicomData.id</t>
   </si>
   <si>
@@ -1164,6 +1168,10 @@
   </si>
   <si>
     <t>Möjlighet att svara med en bild i något av de tillåtna formaten enligt HL7 multimediatyper (inkl. PDF).</t>
+  </si>
+  <si>
+    <t>getimagingoutcome-imagedata-choice:Ett och endast ett av value och reference ska anges {value.exists() xor reference.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMImagingOutcome.imagingOutcome.imagingOutcomeBody.imageRecording.imageStructuredData.imageData.id</t>
@@ -12280,15 +12288,15 @@
         <v>72</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12385,10 +12393,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12487,10 +12495,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12591,10 +12599,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12620,10 +12628,10 @@
         <v>113</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12674,7 +12682,7 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -12691,10 +12699,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12717,13 +12725,13 @@
         <v>72</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12774,7 +12782,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -12791,10 +12799,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12817,13 +12825,13 @@
         <v>72</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12874,7 +12882,7 @@
         <v>72</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -12891,10 +12899,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12920,10 +12928,10 @@
         <v>78</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12974,7 +12982,7 @@
         <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12991,10 +12999,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13091,10 +13099,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13193,10 +13201,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13297,10 +13305,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13326,10 +13334,10 @@
         <v>228</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13380,7 +13388,7 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>73</v>
@@ -13397,10 +13405,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13426,10 +13434,10 @@
         <v>228</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13480,7 +13488,7 @@
         <v>72</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>73</v>
@@ -13497,10 +13505,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13526,10 +13534,10 @@
         <v>123</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13580,7 +13588,7 @@
         <v>72</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>73</v>
@@ -13597,10 +13605,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13626,10 +13634,10 @@
         <v>146</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13680,7 +13688,7 @@
         <v>72</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>73</v>
@@ -13697,10 +13705,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13726,10 +13734,10 @@
         <v>113</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -13780,7 +13788,7 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>73</v>
@@ -13797,10 +13805,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13826,10 +13834,10 @@
         <v>228</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13880,7 +13888,7 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>73</v>
@@ -13897,10 +13905,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13926,10 +13934,10 @@
         <v>113</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13980,7 +13988,7 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>73</v>
@@ -13997,10 +14005,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14026,10 +14034,10 @@
         <v>78</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14080,7 +14088,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -14092,15 +14100,15 @@
         <v>72</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14197,10 +14205,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14299,10 +14307,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14403,10 +14411,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14432,10 +14440,10 @@
         <v>113</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14486,7 +14494,7 @@
         <v>72</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -14503,10 +14511,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14529,13 +14537,13 @@
         <v>72</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14586,7 +14594,7 @@
         <v>72</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>73</v>
@@ -14603,10 +14611,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14629,13 +14637,13 @@
         <v>72</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14686,7 +14694,7 @@
         <v>72</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>73</v>
@@ -14703,10 +14711,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14732,10 +14740,10 @@
         <v>195</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14786,7 +14794,7 @@
         <v>72</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>73</v>
@@ -14803,10 +14811,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14832,10 +14840,10 @@
         <v>78</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14886,7 +14894,7 @@
         <v>72</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>73</v>
@@ -14903,10 +14911,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15003,10 +15011,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15105,10 +15113,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15209,10 +15217,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15238,10 +15246,10 @@
         <v>113</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15292,7 +15300,7 @@
         <v>72</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>83</v>
@@ -15309,10 +15317,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15338,10 +15346,10 @@
         <v>113</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15392,7 +15400,7 @@
         <v>72</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>73</v>
@@ -15409,10 +15417,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15438,10 +15446,10 @@
         <v>113</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15492,7 +15500,7 @@
         <v>72</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>73</v>
@@ -15509,10 +15517,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15541,7 +15549,7 @@
         <v>199</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -15592,7 +15600,7 @@
         <v>72</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>73</v>
@@ -15609,10 +15617,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15638,10 +15646,10 @@
         <v>78</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -15692,7 +15700,7 @@
         <v>72</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>83</v>
@@ -15709,10 +15717,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15809,10 +15817,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15911,10 +15919,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16015,10 +16023,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16047,7 +16055,7 @@
         <v>137</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16098,7 +16106,7 @@
         <v>72</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
@@ -16115,10 +16123,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16147,7 +16155,7 @@
         <v>140</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16198,7 +16206,7 @@
         <v>72</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>73</v>
@@ -16215,10 +16223,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16247,7 +16255,7 @@
         <v>143</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16298,7 +16306,7 @@
         <v>72</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>73</v>
@@ -16315,10 +16323,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16347,7 +16355,7 @@
         <v>147</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -16398,7 +16406,7 @@
         <v>72</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>73</v>
@@ -16415,10 +16423,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16444,10 +16452,10 @@
         <v>78</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16498,7 +16506,7 @@
         <v>72</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
@@ -16515,10 +16523,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16615,10 +16623,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16717,10 +16725,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16821,10 +16829,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16853,7 +16861,7 @@
         <v>156</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16904,7 +16912,7 @@
         <v>72</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>83</v>
@@ -16921,10 +16929,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16953,7 +16961,7 @@
         <v>159</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17004,7 +17012,7 @@
         <v>72</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>83</v>
@@ -17021,10 +17029,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17104,7 +17112,7 @@
         <v>72</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>73</v>
@@ -17121,10 +17129,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17153,7 +17161,7 @@
         <v>165</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17204,7 +17212,7 @@
         <v>72</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>73</v>
@@ -17221,10 +17229,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17253,7 +17261,7 @@
         <v>168</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17304,7 +17312,7 @@
         <v>72</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>73</v>
@@ -17321,10 +17329,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17353,7 +17361,7 @@
         <v>171</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17404,7 +17412,7 @@
         <v>72</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>73</v>
@@ -17421,10 +17429,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17504,7 +17512,7 @@
         <v>72</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>73</v>
@@ -17521,10 +17529,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17604,7 +17612,7 @@
         <v>72</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>73</v>
@@ -17621,10 +17629,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17650,10 +17658,10 @@
         <v>78</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17704,7 +17712,7 @@
         <v>72</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>73</v>
@@ -17721,10 +17729,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17821,10 +17829,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17923,10 +17931,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18027,10 +18035,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18056,10 +18064,10 @@
         <v>123</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18110,7 +18118,7 @@
         <v>72</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>83</v>
@@ -18127,10 +18135,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18159,7 +18167,7 @@
         <v>140</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18210,7 +18218,7 @@
         <v>72</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>73</v>
@@ -18227,10 +18235,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18259,7 +18267,7 @@
         <v>143</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -18310,7 +18318,7 @@
         <v>72</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>73</v>
@@ -18327,10 +18335,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18410,7 +18418,7 @@
         <v>72</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>73</v>
@@ -18427,10 +18435,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18456,10 +18464,10 @@
         <v>78</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18510,7 +18518,7 @@
         <v>72</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>83</v>
@@ -18527,10 +18535,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18627,10 +18635,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18729,10 +18737,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18833,10 +18841,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18862,10 +18870,10 @@
         <v>113</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -18916,7 +18924,7 @@
         <v>72</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -18933,10 +18941,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18962,10 +18970,10 @@
         <v>113</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19016,7 +19024,7 @@
         <v>72</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>73</v>
@@ -19033,10 +19041,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19062,10 +19070,10 @@
         <v>113</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19116,7 +19124,7 @@
         <v>72</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -19133,10 +19141,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19162,10 +19170,10 @@
         <v>113</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19216,7 +19224,7 @@
         <v>72</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>73</v>
@@ -19233,10 +19241,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19262,10 +19270,10 @@
         <v>113</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19316,7 +19324,7 @@
         <v>72</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMImagingOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
